--- a/ListeOZdisan.xlsx
+++ b/ListeOZdisan.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="879">
   <si>
     <t>#</t>
   </si>
@@ -2613,6 +2613,57 @@
   </si>
   <si>
     <t>230</t>
+  </si>
+  <si>
+    <t>IC-2596 V.REG.3A 3.3V STEP-DOWN TO-263-5L</t>
+  </si>
+  <si>
+    <t>LM2596R-3.3-HTC</t>
+  </si>
+  <si>
+    <t>IC-2596 V.REG.3A 5V STEP-DOWN TO-263-5L</t>
+  </si>
+  <si>
+    <t>LM2596R-5.0-HTC</t>
+  </si>
+  <si>
+    <t>DIODE TVS 3kW 30V DO214AB (SMC) Bi-Direction SMT</t>
+  </si>
+  <si>
+    <t>SMDJ30CA/TR7</t>
+  </si>
+  <si>
+    <t>DIODE TVS 400W 30V DO214AC (SMA) Uni-Direction SMT</t>
+  </si>
+  <si>
+    <t>SMAJ30AY-TKS</t>
+  </si>
+  <si>
+    <t>DIODE TVS 600W 30V DO214AA (SMB) Uni-Direction SMT</t>
+  </si>
+  <si>
+    <t>P6SMBJ30A_R2_00001</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>232</t>
+  </si>
+  <si>
+    <t>K-231026</t>
+  </si>
+  <si>
+    <t>K-231027</t>
+  </si>
+  <si>
+    <t>K-231028</t>
+  </si>
+  <si>
+    <t>K-231029</t>
+  </si>
+  <si>
+    <t>K-231030</t>
   </si>
 </sst>
 </file>
@@ -2626,11 +2677,19 @@
     <numFmt numFmtId="167" formatCode="&quot;₺&quot;#,##0.000"/>
     <numFmt numFmtId="168" formatCode="[$$-409]#,##0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="162"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="162"/>
       <scheme val="minor"/>
     </font>
@@ -2729,20 +2788,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2777,18 +2836,31 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2817,8 +2889,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Products" displayName="Products" ref="A1:H332" totalsRowShown="0">
-  <autoFilter ref="A1:H332">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Products" displayName="Products" ref="A1:H337" totalsRowShown="0">
+  <autoFilter ref="A1:H337">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -3103,7 +3175,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H332"/>
+  <dimension ref="A1:H337"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.140625" style="1" customWidth="1"/>
@@ -3418,10 +3490,10 @@
       <c r="E12" s="7">
         <v>50</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="13">
         <v>0.16721</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="13">
         <v>10.032</v>
       </c>
       <c r="H12" s="20" t="s">
@@ -3444,10 +3516,10 @@
       <c r="E13" s="7">
         <v>5</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="13">
         <v>1.5529999999999999</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="13">
         <v>9.3239999999999998</v>
       </c>
       <c r="H13" s="20" t="s">
@@ -3470,10 +3542,10 @@
       <c r="E14" s="7">
         <v>1</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="13">
         <v>9.1701899999999998</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="13">
         <v>11.004</v>
       </c>
       <c r="H14" s="20" t="s">
@@ -3496,10 +3568,10 @@
       <c r="E15" s="7">
         <v>100</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="13">
         <v>5.475E-2</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="13">
         <v>6.5759999999999996</v>
       </c>
       <c r="H15" s="20" t="s">
@@ -3522,10 +3594,10 @@
       <c r="E16" s="7">
         <v>100</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="13">
         <v>5.475E-2</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="13">
         <v>6.5759999999999996</v>
       </c>
       <c r="H16" s="20" t="s">
@@ -6360,7 +6432,7 @@
         <f>Products[[#This Row],[Birim Fiyat]]*Products[[#This Row],[Adet]]</f>
         <v>63.4</v>
       </c>
-      <c r="H133" s="20" t="s">
+      <c r="H133" s="30" t="s">
         <v>447</v>
       </c>
     </row>
@@ -9922,6 +9994,136 @@
       <c r="G332" s="26"/>
       <c r="H332" t="s">
         <v>759</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8">
+      <c r="A333" s="14">
+        <v>231</v>
+      </c>
+      <c r="B333" s="8" t="s">
+        <v>871</v>
+      </c>
+      <c r="C333" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="D333" s="7" t="s">
+        <v>870</v>
+      </c>
+      <c r="E333" s="28">
+        <v>30</v>
+      </c>
+      <c r="F333" s="13">
+        <v>4.6129600000000002</v>
+      </c>
+      <c r="G333" s="10">
+        <v>166.06800000000001</v>
+      </c>
+      <c r="H333" s="31" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8">
+      <c r="A334" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="B334" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="C334" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D334" s="7" t="s">
+        <v>868</v>
+      </c>
+      <c r="E334" s="28">
+        <v>20</v>
+      </c>
+      <c r="F334" s="13">
+        <v>3.0163199999999999</v>
+      </c>
+      <c r="G334" s="10">
+        <v>72.396000000000001</v>
+      </c>
+      <c r="H334" s="31" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8">
+      <c r="A335" s="14">
+        <v>232</v>
+      </c>
+      <c r="B335" s="8" t="s">
+        <v>867</v>
+      </c>
+      <c r="C335" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D335" s="7" t="s">
+        <v>866</v>
+      </c>
+      <c r="E335" s="28">
+        <v>10</v>
+      </c>
+      <c r="F335" s="13">
+        <v>10.1683</v>
+      </c>
+      <c r="G335" s="10">
+        <v>122.01600000000001</v>
+      </c>
+      <c r="H335" s="31" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8">
+      <c r="A336" s="7" t="s">
+        <v>873</v>
+      </c>
+      <c r="B336" s="8" t="s">
+        <v>865</v>
+      </c>
+      <c r="C336" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="D336" s="7" t="s">
+        <v>864</v>
+      </c>
+      <c r="E336" s="28">
+        <v>2</v>
+      </c>
+      <c r="F336" s="13">
+        <v>67.420100000000005</v>
+      </c>
+      <c r="G336" s="10">
+        <v>161.80799999999999</v>
+      </c>
+      <c r="H336" s="31" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8">
+      <c r="A337" s="14">
+        <v>233</v>
+      </c>
+      <c r="B337" s="15" t="s">
+        <v>863</v>
+      </c>
+      <c r="C337" s="15" t="s">
+        <v>360</v>
+      </c>
+      <c r="D337" s="14" t="s">
+        <v>862</v>
+      </c>
+      <c r="E337" s="29">
+        <v>5</v>
+      </c>
+      <c r="F337" s="16">
+        <v>40.936100000000003</v>
+      </c>
+      <c r="G337" s="27">
+        <v>245.61600000000001</v>
+      </c>
+      <c r="H337" s="31" t="s">
+        <v>878</v>
       </c>
     </row>
   </sheetData>
